--- a/artfynd/A 7916-2026 artfynd.xlsx
+++ b/artfynd/A 7916-2026 artfynd.xlsx
@@ -2430,32 +2430,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131523887</v>
+        <v>131523877</v>
       </c>
       <c r="B19" t="n">
-        <v>58047</v>
+        <v>57076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,7 +2463,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>370005</v>
+        <v>369712</v>
       </c>
       <c r="R19" t="n">
-        <v>6871091</v>
+        <v>6870931</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,41 +2535,40 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131523916</v>
+        <v>131523887</v>
       </c>
       <c r="B20" t="n">
-        <v>8451</v>
+        <v>58047</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2579,10 +2578,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>370134</v>
+        <v>370005</v>
       </c>
       <c r="R20" t="n">
-        <v>6870717</v>
+        <v>6871091</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,12 +2608,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2623,7 +2622,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2642,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131523877</v>
+        <v>131523916</v>
       </c>
       <c r="B21" t="n">
-        <v>57076</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2653,29 +2651,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2685,10 +2684,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>369712</v>
+        <v>370134</v>
       </c>
       <c r="R21" t="n">
-        <v>6870931</v>
+        <v>6870717</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,12 +2714,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2729,6 +2728,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131523909</v>
+        <v>131523881</v>
       </c>
       <c r="B36" t="n">
-        <v>57079</v>
+        <v>91781</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,42 +4196,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102613</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>370145</v>
+        <v>370376</v>
       </c>
       <c r="R36" t="n">
-        <v>6871436</v>
+        <v>6870594</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4272,6 +4264,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4290,10 +4283,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131523866</v>
+        <v>131523909</v>
       </c>
       <c r="B37" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4301,21 +4294,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4323,7 +4316,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4333,10 +4326,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>370356</v>
+        <v>370145</v>
       </c>
       <c r="R37" t="n">
-        <v>6870757</v>
+        <v>6871436</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4395,10 +4388,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131523939</v>
+        <v>131523866</v>
       </c>
       <c r="B38" t="n">
-        <v>8451</v>
+        <v>57076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4406,30 +4399,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4439,10 +4431,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>370247</v>
+        <v>370356</v>
       </c>
       <c r="R38" t="n">
-        <v>6870981</v>
+        <v>6870757</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4483,7 +4475,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4502,45 +4493,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131523912</v>
+        <v>131523939</v>
       </c>
       <c r="B39" t="n">
-        <v>79008</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>370180</v>
+        <v>370247</v>
       </c>
       <c r="R39" t="n">
-        <v>6871374</v>
+        <v>6870981</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4581,6 +4581,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4599,10 +4600,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131523838</v>
+        <v>131523912</v>
       </c>
       <c r="B40" t="n">
-        <v>79840</v>
+        <v>79008</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4610,21 +4611,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4634,10 +4635,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>370372</v>
+        <v>370180</v>
       </c>
       <c r="R40" t="n">
-        <v>6870597</v>
+        <v>6871374</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4696,32 +4697,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131523881</v>
+        <v>131523838</v>
       </c>
       <c r="B41" t="n">
-        <v>91781</v>
+        <v>79840</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4731,10 +4732,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>370376</v>
+        <v>370372</v>
       </c>
       <c r="R41" t="n">
-        <v>6870594</v>
+        <v>6870597</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4775,7 +4776,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -6324,10 +6324,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131523844</v>
+        <v>131523857</v>
       </c>
       <c r="B57" t="n">
-        <v>79840</v>
+        <v>79345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6335,34 +6335,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>370034</v>
+        <v>370023</v>
       </c>
       <c r="R57" t="n">
-        <v>6871209</v>
+        <v>6871137</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6403,6 +6406,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6421,54 +6425,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131523944</v>
+        <v>131523844</v>
       </c>
       <c r="B58" t="n">
-        <v>8451</v>
+        <v>79840</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>369995</v>
+        <v>370034</v>
       </c>
       <c r="R58" t="n">
-        <v>6871251</v>
+        <v>6871209</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6509,7 +6504,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6528,37 +6522,43 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131523857</v>
+        <v>131523944</v>
       </c>
       <c r="B59" t="n">
-        <v>79345</v>
+        <v>8451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>967</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6566,10 +6566,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>370023</v>
+        <v>369995</v>
       </c>
       <c r="R59" t="n">
-        <v>6871137</v>
+        <v>6871251</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 7916-2026 artfynd.xlsx
+++ b/artfynd/A 7916-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131523874</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131523873</v>
       </c>
       <c r="B3" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131523942</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>131523940</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131523839</v>
       </c>
       <c r="B6" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>131523872</v>
       </c>
       <c r="B7" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>131523897</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>131523941</v>
       </c>
       <c r="B9" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>131523902</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>131523919</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>131523956</v>
       </c>
       <c r="B12" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>131523884</v>
       </c>
       <c r="B13" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>131523853</v>
       </c>
       <c r="B14" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>131523835</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>131523921</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>131523883</v>
       </c>
       <c r="B17" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>131523983</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>131523877</v>
       </c>
       <c r="B19" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,40 +2535,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131523887</v>
+        <v>131523916</v>
       </c>
       <c r="B20" t="n">
-        <v>58047</v>
+        <v>8453</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2578,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>370005</v>
+        <v>370134</v>
       </c>
       <c r="R20" t="n">
-        <v>6871091</v>
+        <v>6870717</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2608,12 +2609,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2622,6 +2623,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2640,41 +2642,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131523916</v>
+        <v>131523887</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>58050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2684,10 +2685,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>370134</v>
+        <v>370005</v>
       </c>
       <c r="R21" t="n">
-        <v>6870717</v>
+        <v>6871091</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2714,12 +2715,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2728,7 +2729,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>131523904</v>
       </c>
       <c r="B22" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>131523885</v>
       </c>
       <c r="B23" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2957,45 +2957,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131523837</v>
+        <v>131523948</v>
       </c>
       <c r="B24" t="n">
-        <v>79840</v>
+        <v>8453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>370168</v>
+        <v>369730</v>
       </c>
       <c r="R24" t="n">
-        <v>6870859</v>
+        <v>6870912</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,12 +3031,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3036,6 +3045,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3057,7 +3067,7 @@
         <v>131523903</v>
       </c>
       <c r="B25" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3159,54 +3169,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131523948</v>
+        <v>131523837</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>369730</v>
+        <v>370168</v>
       </c>
       <c r="R26" t="n">
-        <v>6870912</v>
+        <v>6870859</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,12 +3234,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3247,7 +3248,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>131523978</v>
       </c>
       <c r="B27" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>131523854</v>
       </c>
       <c r="B28" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>131523955</v>
       </c>
       <c r="B29" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>131523987</v>
       </c>
       <c r="B30" t="n">
-        <v>78257</v>
+        <v>78260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>131523856</v>
       </c>
       <c r="B31" t="n">
-        <v>79345</v>
+        <v>79348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131523917</v>
+        <v>131523918</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>370100</v>
+        <v>370157</v>
       </c>
       <c r="R32" t="n">
-        <v>6870761</v>
+        <v>6870753</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
         <v>131523920</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131523918</v>
+        <v>131523917</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>370157</v>
+        <v>370100</v>
       </c>
       <c r="R34" t="n">
-        <v>6870753</v>
+        <v>6870761</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4083,7 +4083,7 @@
         <v>131523894</v>
       </c>
       <c r="B35" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131523881</v>
+        <v>131523866</v>
       </c>
       <c r="B36" t="n">
-        <v>91781</v>
+        <v>57079</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,34 +4196,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>370376</v>
+        <v>370356</v>
       </c>
       <c r="R36" t="n">
-        <v>6870594</v>
+        <v>6870757</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4264,7 +4272,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4283,10 +4290,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131523909</v>
+        <v>131523881</v>
       </c>
       <c r="B37" t="n">
-        <v>57079</v>
+        <v>91784</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4294,42 +4301,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102613</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>370145</v>
+        <v>370376</v>
       </c>
       <c r="R37" t="n">
-        <v>6871436</v>
+        <v>6870594</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4370,6 +4369,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4388,53 +4388,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131523866</v>
+        <v>131523838</v>
       </c>
       <c r="B38" t="n">
-        <v>57076</v>
+        <v>79843</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>370356</v>
+        <v>370372</v>
       </c>
       <c r="R38" t="n">
-        <v>6870757</v>
+        <v>6870597</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4496,7 +4488,7 @@
         <v>131523939</v>
       </c>
       <c r="B39" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4603,7 +4595,7 @@
         <v>131523912</v>
       </c>
       <c r="B40" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4697,45 +4689,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131523838</v>
+        <v>131523909</v>
       </c>
       <c r="B41" t="n">
-        <v>79840</v>
+        <v>57082</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>370372</v>
+        <v>370145</v>
       </c>
       <c r="R41" t="n">
-        <v>6870597</v>
+        <v>6871436</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131523860</v>
+        <v>131523954</v>
       </c>
       <c r="B42" t="n">
-        <v>57888</v>
+        <v>79010</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4805,42 +4805,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>370137</v>
+        <v>370056</v>
       </c>
       <c r="R42" t="n">
-        <v>6871198</v>
+        <v>6871149</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4899,10 +4891,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131523954</v>
+        <v>131523860</v>
       </c>
       <c r="B43" t="n">
-        <v>79007</v>
+        <v>57891</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4910,34 +4902,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>370056</v>
+        <v>370137</v>
       </c>
       <c r="R43" t="n">
-        <v>6871149</v>
+        <v>6871198</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,7 +4999,7 @@
         <v>131523938</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131523858</v>
+        <v>131523901</v>
       </c>
       <c r="B45" t="n">
         <v>57888</v>
@@ -5114,16 +5114,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5132,16 +5132,24 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>370140</v>
+        <v>370048</v>
       </c>
       <c r="R45" t="n">
-        <v>6871199</v>
+        <v>6871142</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5174,11 +5182,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>16.49 färska spår</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5205,45 +5208,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131523836</v>
+        <v>131523867</v>
       </c>
       <c r="B46" t="n">
-        <v>79869</v>
+        <v>57079</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>370167</v>
+        <v>370351</v>
       </c>
       <c r="R46" t="n">
-        <v>6871437</v>
+        <v>6870757</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5302,10 +5313,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131523901</v>
+        <v>131523836</v>
       </c>
       <c r="B47" t="n">
-        <v>57885</v>
+        <v>79872</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5313,42 +5324,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>370048</v>
+        <v>370167</v>
       </c>
       <c r="R47" t="n">
-        <v>6871142</v>
+        <v>6871437</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5407,53 +5410,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131523867</v>
+        <v>131523858</v>
       </c>
       <c r="B48" t="n">
-        <v>57076</v>
+        <v>57891</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>370351</v>
+        <v>370140</v>
       </c>
       <c r="R48" t="n">
-        <v>6870757</v>
+        <v>6871199</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5486,6 +5481,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>16.49 färska spår</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5515,7 +5515,7 @@
         <v>131523871</v>
       </c>
       <c r="B49" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>131523945</v>
       </c>
       <c r="B50" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>131523943</v>
       </c>
       <c r="B51" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>131523851</v>
       </c>
       <c r="B52" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131523913</v>
+        <v>131523852</v>
       </c>
       <c r="B53" t="n">
-        <v>79008</v>
+        <v>79843</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>370001</v>
+        <v>370027</v>
       </c>
       <c r="R53" t="n">
-        <v>6871269</v>
+        <v>6871131</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6025,10 +6025,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131523852</v>
+        <v>131523913</v>
       </c>
       <c r="B54" t="n">
-        <v>79840</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6036,21 +6036,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>370027</v>
+        <v>370001</v>
       </c>
       <c r="R54" t="n">
-        <v>6871131</v>
+        <v>6871269</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6125,7 +6125,7 @@
         <v>131523886</v>
       </c>
       <c r="B55" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>131523979</v>
       </c>
       <c r="B56" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>131523857</v>
       </c>
       <c r="B57" t="n">
-        <v>79345</v>
+        <v>79348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6425,45 +6425,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131523844</v>
+        <v>131523944</v>
       </c>
       <c r="B58" t="n">
-        <v>79840</v>
+        <v>8453</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>370034</v>
+        <v>369995</v>
       </c>
       <c r="R58" t="n">
-        <v>6871209</v>
+        <v>6871251</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6504,6 +6513,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6522,54 +6532,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131523944</v>
+        <v>131523844</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>79843</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>369995</v>
+        <v>370034</v>
       </c>
       <c r="R59" t="n">
-        <v>6871251</v>
+        <v>6871209</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6610,7 +6611,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6629,53 +6629,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131523879</v>
+        <v>131523982</v>
       </c>
       <c r="B60" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>370181</v>
+        <v>369987</v>
       </c>
       <c r="R60" t="n">
-        <v>6871322</v>
+        <v>6871384</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6708,11 +6700,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska spår i snön.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6739,45 +6726,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131523982</v>
+        <v>131523879</v>
       </c>
       <c r="B61" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>369987</v>
+        <v>370181</v>
       </c>
       <c r="R61" t="n">
-        <v>6871384</v>
+        <v>6871322</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6810,6 +6805,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska spår i snön.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6839,7 +6839,7 @@
         <v>131523878</v>
       </c>
       <c r="B62" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6941,45 +6941,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131523847</v>
+        <v>131523947</v>
       </c>
       <c r="B63" t="n">
-        <v>79840</v>
+        <v>8453</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>370084</v>
+        <v>370037</v>
       </c>
       <c r="R63" t="n">
-        <v>6871179</v>
+        <v>6871188</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7020,6 +7029,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7038,54 +7048,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131523947</v>
+        <v>131523847</v>
       </c>
       <c r="B64" t="n">
-        <v>8451</v>
+        <v>79843</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>370037</v>
+        <v>370084</v>
       </c>
       <c r="R64" t="n">
-        <v>6871188</v>
+        <v>6871179</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7126,7 +7127,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7145,10 +7145,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131523842</v>
+        <v>131523981</v>
       </c>
       <c r="B65" t="n">
-        <v>79840</v>
+        <v>79253</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7156,21 +7156,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>370085</v>
+        <v>370036</v>
       </c>
       <c r="R65" t="n">
-        <v>6871463</v>
+        <v>6871407</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7242,10 +7242,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131523981</v>
+        <v>131523842</v>
       </c>
       <c r="B66" t="n">
-        <v>79250</v>
+        <v>79843</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7253,21 +7253,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7277,10 +7277,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>370036</v>
+        <v>370085</v>
       </c>
       <c r="R66" t="n">
-        <v>6871407</v>
+        <v>6871463</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7342,7 +7342,7 @@
         <v>131523980</v>
       </c>
       <c r="B67" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7436,10 +7436,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131523936</v>
+        <v>131523876</v>
       </c>
       <c r="B68" t="n">
-        <v>8451</v>
+        <v>57079</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7447,30 +7447,29 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7480,10 +7479,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>370347</v>
+        <v>370067</v>
       </c>
       <c r="R68" t="n">
-        <v>6870585</v>
+        <v>6871433</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,13 +7517,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska spår i snön</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7543,53 +7546,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131523876</v>
+        <v>131523848</v>
       </c>
       <c r="B69" t="n">
-        <v>57076</v>
+        <v>79843</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>370067</v>
+        <v>370077</v>
       </c>
       <c r="R69" t="n">
-        <v>6871433</v>
+        <v>6871172</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7622,11 +7617,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska spår i snön</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7653,10 +7643,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131523848</v>
+        <v>131523855</v>
       </c>
       <c r="B70" t="n">
-        <v>79840</v>
+        <v>79348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7664,34 +7654,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>370077</v>
+        <v>370088</v>
       </c>
       <c r="R70" t="n">
-        <v>6871172</v>
+        <v>6871179</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7732,6 +7725,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7750,37 +7744,43 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131523855</v>
+        <v>131523936</v>
       </c>
       <c r="B71" t="n">
-        <v>79345</v>
+        <v>8453</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>967</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>370088</v>
+        <v>370347</v>
       </c>
       <c r="R71" t="n">
-        <v>6871179</v>
+        <v>6870585</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7854,7 +7854,7 @@
         <v>131523900</v>
       </c>
       <c r="B72" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>131523841</v>
       </c>
       <c r="B73" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>131523869</v>
       </c>
       <c r="B74" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>131523865</v>
       </c>
       <c r="B75" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>131523840</v>
       </c>
       <c r="B76" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8365,53 +8365,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131523910</v>
+        <v>131523846</v>
       </c>
       <c r="B77" t="n">
-        <v>57079</v>
+        <v>79843</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>370022</v>
+        <v>370030</v>
       </c>
       <c r="R77" t="n">
-        <v>6871195</v>
+        <v>6871190</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8470,10 +8462,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131523846</v>
+        <v>131523843</v>
       </c>
       <c r="B78" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8505,10 +8497,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>370030</v>
+        <v>370001</v>
       </c>
       <c r="R78" t="n">
-        <v>6871190</v>
+        <v>6871269</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8567,45 +8559,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131523843</v>
+        <v>131523910</v>
       </c>
       <c r="B79" t="n">
-        <v>79840</v>
+        <v>57082</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>370001</v>
+        <v>370022</v>
       </c>
       <c r="R79" t="n">
-        <v>6871269</v>
+        <v>6871195</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>131523908</v>
       </c>
       <c r="B80" t="n">
-        <v>57079</v>
+        <v>57082</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>131523977</v>
       </c>
       <c r="B81" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 7916-2026 artfynd.xlsx
+++ b/artfynd/A 7916-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131523874</v>
       </c>
       <c r="B2" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131523873</v>
       </c>
       <c r="B3" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -992,54 +992,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131523940</v>
+        <v>131523839</v>
       </c>
       <c r="B5" t="n">
-        <v>8453</v>
+        <v>79844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>370206</v>
+        <v>370168</v>
       </c>
       <c r="R5" t="n">
-        <v>6871044</v>
+        <v>6871266</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1071,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,45 +1089,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131523839</v>
+        <v>131523940</v>
       </c>
       <c r="B6" t="n">
-        <v>79843</v>
+        <v>8453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>370168</v>
+        <v>370206</v>
       </c>
       <c r="R6" t="n">
-        <v>6871266</v>
+        <v>6871044</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,6 +1177,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>131523872</v>
       </c>
       <c r="B7" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>131523897</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>131523902</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>131523956</v>
       </c>
       <c r="B12" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>131523884</v>
       </c>
       <c r="B13" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>131523853</v>
       </c>
       <c r="B14" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>131523835</v>
       </c>
       <c r="B15" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>131523883</v>
       </c>
       <c r="B17" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>131523983</v>
       </c>
       <c r="B18" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>131523877</v>
       </c>
       <c r="B19" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,41 +2535,40 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131523916</v>
+        <v>131523887</v>
       </c>
       <c r="B20" t="n">
-        <v>8453</v>
+        <v>58051</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2579,10 +2578,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>370134</v>
+        <v>370005</v>
       </c>
       <c r="R20" t="n">
-        <v>6870717</v>
+        <v>6871091</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,12 +2608,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2623,7 +2622,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2642,40 +2640,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131523887</v>
+        <v>131523916</v>
       </c>
       <c r="B21" t="n">
-        <v>58050</v>
+        <v>8453</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2685,10 +2684,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>370005</v>
+        <v>370134</v>
       </c>
       <c r="R21" t="n">
-        <v>6871091</v>
+        <v>6870717</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,12 +2714,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2729,6 +2728,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>131523904</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>131523885</v>
       </c>
       <c r="B23" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131523903</v>
+        <v>131523837</v>
       </c>
       <c r="B25" t="n">
-        <v>57888</v>
+        <v>79844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3075,42 +3075,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>369860</v>
+        <v>370168</v>
       </c>
       <c r="R25" t="n">
-        <v>6870883</v>
+        <v>6870859</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3137,12 +3129,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3169,10 +3161,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131523837</v>
+        <v>131523903</v>
       </c>
       <c r="B26" t="n">
-        <v>79843</v>
+        <v>57889</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3180,34 +3172,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>370168</v>
+        <v>369860</v>
       </c>
       <c r="R26" t="n">
-        <v>6870859</v>
+        <v>6870883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3269,7 +3269,7 @@
         <v>131523978</v>
       </c>
       <c r="B27" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>131523854</v>
       </c>
       <c r="B28" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>131523955</v>
       </c>
       <c r="B29" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>131523987</v>
       </c>
       <c r="B30" t="n">
-        <v>78260</v>
+        <v>78261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>131523856</v>
       </c>
       <c r="B31" t="n">
-        <v>79348</v>
+        <v>79349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131523918</v>
+        <v>131523917</v>
       </c>
       <c r="B32" t="n">
         <v>8453</v>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>370157</v>
+        <v>370100</v>
       </c>
       <c r="R32" t="n">
-        <v>6870753</v>
+        <v>6870761</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131523917</v>
+        <v>131523918</v>
       </c>
       <c r="B34" t="n">
         <v>8453</v>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>370100</v>
+        <v>370157</v>
       </c>
       <c r="R34" t="n">
-        <v>6870761</v>
+        <v>6870753</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4083,7 +4083,7 @@
         <v>131523894</v>
       </c>
       <c r="B35" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131523866</v>
+        <v>131523881</v>
       </c>
       <c r="B36" t="n">
-        <v>57079</v>
+        <v>91785</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,42 +4196,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>370356</v>
+        <v>370376</v>
       </c>
       <c r="R36" t="n">
-        <v>6870757</v>
+        <v>6870594</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4272,6 +4264,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4290,10 +4283,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131523881</v>
+        <v>131523866</v>
       </c>
       <c r="B37" t="n">
-        <v>91784</v>
+        <v>57080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4301,34 +4294,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>370376</v>
+        <v>370356</v>
       </c>
       <c r="R37" t="n">
-        <v>6870594</v>
+        <v>6870757</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4369,7 +4370,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4388,45 +4388,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131523838</v>
+        <v>131523909</v>
       </c>
       <c r="B38" t="n">
-        <v>79843</v>
+        <v>57083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>370372</v>
+        <v>370145</v>
       </c>
       <c r="R38" t="n">
-        <v>6870597</v>
+        <v>6871436</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4603,7 @@
         <v>131523912</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>79012</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4689,53 +4697,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131523909</v>
+        <v>131523838</v>
       </c>
       <c r="B41" t="n">
-        <v>57082</v>
+        <v>79844</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>370145</v>
+        <v>370372</v>
       </c>
       <c r="R41" t="n">
-        <v>6871436</v>
+        <v>6870597</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131523954</v>
+        <v>131523860</v>
       </c>
       <c r="B42" t="n">
-        <v>79010</v>
+        <v>57892</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4805,34 +4805,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>370056</v>
+        <v>370137</v>
       </c>
       <c r="R42" t="n">
-        <v>6871149</v>
+        <v>6871198</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4891,40 +4899,41 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131523860</v>
+        <v>131523938</v>
       </c>
       <c r="B43" t="n">
-        <v>57891</v>
+        <v>8453</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4934,10 +4943,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>370137</v>
+        <v>370347</v>
       </c>
       <c r="R43" t="n">
-        <v>6871198</v>
+        <v>6870809</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4978,6 +4987,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4996,54 +5006,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131523938</v>
+        <v>131523954</v>
       </c>
       <c r="B44" t="n">
-        <v>8453</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>370347</v>
+        <v>370056</v>
       </c>
       <c r="R44" t="n">
-        <v>6870809</v>
+        <v>6871149</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5084,7 +5085,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131523901</v>
+        <v>131523836</v>
       </c>
       <c r="B45" t="n">
-        <v>57888</v>
+        <v>79873</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5114,42 +5114,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>370048</v>
+        <v>370167</v>
       </c>
       <c r="R45" t="n">
-        <v>6871142</v>
+        <v>6871437</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5208,32 +5200,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131523867</v>
+        <v>131523901</v>
       </c>
       <c r="B46" t="n">
-        <v>57079</v>
+        <v>57889</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5241,7 +5233,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5251,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>370351</v>
+        <v>370048</v>
       </c>
       <c r="R46" t="n">
-        <v>6870757</v>
+        <v>6871142</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5313,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131523836</v>
+        <v>131523858</v>
       </c>
       <c r="B47" t="n">
-        <v>79872</v>
+        <v>57892</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5324,21 +5316,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5348,10 +5340,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>370167</v>
+        <v>370140</v>
       </c>
       <c r="R47" t="n">
-        <v>6871437</v>
+        <v>6871199</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5384,6 +5376,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>16.49 färska spår</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5410,45 +5407,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131523858</v>
+        <v>131523867</v>
       </c>
       <c r="B48" t="n">
-        <v>57891</v>
+        <v>57080</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>370140</v>
+        <v>370351</v>
       </c>
       <c r="R48" t="n">
-        <v>6871199</v>
+        <v>6870757</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5481,11 +5486,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>16.49 färska spår</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5515,7 +5515,7 @@
         <v>131523871</v>
       </c>
       <c r="B49" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>131523851</v>
       </c>
       <c r="B52" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131523852</v>
+        <v>131523913</v>
       </c>
       <c r="B53" t="n">
-        <v>79843</v>
+        <v>79012</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>370027</v>
+        <v>370001</v>
       </c>
       <c r="R53" t="n">
-        <v>6871131</v>
+        <v>6871269</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6025,10 +6025,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131523913</v>
+        <v>131523852</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79844</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6036,21 +6036,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>370001</v>
+        <v>370027</v>
       </c>
       <c r="R54" t="n">
-        <v>6871269</v>
+        <v>6871131</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6125,7 +6125,7 @@
         <v>131523886</v>
       </c>
       <c r="B55" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>131523979</v>
       </c>
       <c r="B56" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>131523857</v>
       </c>
       <c r="B57" t="n">
-        <v>79348</v>
+        <v>79349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>131523844</v>
       </c>
       <c r="B59" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>131523982</v>
       </c>
       <c r="B60" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>131523879</v>
       </c>
       <c r="B61" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>131523878</v>
       </c>
       <c r="B62" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>131523847</v>
       </c>
       <c r="B64" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>131523981</v>
       </c>
       <c r="B65" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>131523842</v>
       </c>
       <c r="B66" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>131523980</v>
       </c>
       <c r="B67" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7436,42 +7436,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131523876</v>
+        <v>131523855</v>
       </c>
       <c r="B68" t="n">
-        <v>57079</v>
+        <v>79349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>967</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7479,10 +7474,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>370067</v>
+        <v>370088</v>
       </c>
       <c r="R68" t="n">
-        <v>6871433</v>
+        <v>6871179</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7517,17 +7512,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska spår i snön</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7546,45 +7537,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131523848</v>
+        <v>131523876</v>
       </c>
       <c r="B69" t="n">
-        <v>79843</v>
+        <v>57080</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>370077</v>
+        <v>370067</v>
       </c>
       <c r="R69" t="n">
-        <v>6871172</v>
+        <v>6871433</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7617,6 +7616,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska spår i snön</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7643,37 +7647,43 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131523855</v>
+        <v>131523936</v>
       </c>
       <c r="B70" t="n">
-        <v>79348</v>
+        <v>8453</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>967</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7681,10 +7691,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>370088</v>
+        <v>370347</v>
       </c>
       <c r="R70" t="n">
-        <v>6871179</v>
+        <v>6870585</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7744,54 +7754,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131523936</v>
+        <v>131523848</v>
       </c>
       <c r="B71" t="n">
-        <v>8453</v>
+        <v>79844</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>370347</v>
+        <v>370077</v>
       </c>
       <c r="R71" t="n">
-        <v>6870585</v>
+        <v>6871172</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7832,7 +7833,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>131523900</v>
       </c>
       <c r="B72" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>131523841</v>
       </c>
       <c r="B73" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>131523869</v>
       </c>
       <c r="B74" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>131523865</v>
       </c>
       <c r="B75" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8268,45 +8268,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131523840</v>
+        <v>131523910</v>
       </c>
       <c r="B76" t="n">
-        <v>79843</v>
+        <v>57083</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>370171</v>
+        <v>370022</v>
       </c>
       <c r="R76" t="n">
-        <v>6871353</v>
+        <v>6871195</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8365,10 +8373,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131523846</v>
+        <v>131523840</v>
       </c>
       <c r="B77" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8400,10 +8408,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>370030</v>
+        <v>370171</v>
       </c>
       <c r="R77" t="n">
-        <v>6871190</v>
+        <v>6871353</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8462,10 +8470,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131523843</v>
+        <v>131523846</v>
       </c>
       <c r="B78" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8497,10 +8505,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>370001</v>
+        <v>370030</v>
       </c>
       <c r="R78" t="n">
-        <v>6871269</v>
+        <v>6871190</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8559,53 +8567,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131523910</v>
+        <v>131523843</v>
       </c>
       <c r="B79" t="n">
-        <v>57082</v>
+        <v>79844</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>370022</v>
+        <v>370001</v>
       </c>
       <c r="R79" t="n">
-        <v>6871195</v>
+        <v>6871269</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>131523908</v>
       </c>
       <c r="B80" t="n">
-        <v>57082</v>
+        <v>57083</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>131523977</v>
       </c>
       <c r="B81" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 7916-2026 artfynd.xlsx
+++ b/artfynd/A 7916-2026 artfynd.xlsx
@@ -4185,32 +4185,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131523881</v>
+        <v>131523912</v>
       </c>
       <c r="B36" t="n">
-        <v>91785</v>
+        <v>79012</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>370376</v>
+        <v>370180</v>
       </c>
       <c r="R36" t="n">
-        <v>6870594</v>
+        <v>6871374</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4264,7 +4264,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4283,10 +4282,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131523866</v>
+        <v>131523881</v>
       </c>
       <c r="B37" t="n">
-        <v>57080</v>
+        <v>91785</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4294,42 +4293,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>370356</v>
+        <v>370376</v>
       </c>
       <c r="R37" t="n">
-        <v>6870757</v>
+        <v>6870594</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4370,6 +4361,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4388,10 +4380,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131523909</v>
+        <v>131523866</v>
       </c>
       <c r="B38" t="n">
-        <v>57083</v>
+        <v>57080</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4399,21 +4391,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4421,7 +4413,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4431,10 +4423,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>370145</v>
+        <v>370356</v>
       </c>
       <c r="R38" t="n">
-        <v>6871436</v>
+        <v>6870757</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4493,10 +4485,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131523939</v>
+        <v>131523909</v>
       </c>
       <c r="B39" t="n">
-        <v>8453</v>
+        <v>57083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4504,30 +4496,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>102613</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4537,10 +4528,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>370247</v>
+        <v>370145</v>
       </c>
       <c r="R39" t="n">
-        <v>6870981</v>
+        <v>6871436</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4581,7 +4572,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4600,45 +4590,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131523912</v>
+        <v>131523939</v>
       </c>
       <c r="B40" t="n">
-        <v>79012</v>
+        <v>8453</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>370180</v>
+        <v>370247</v>
       </c>
       <c r="R40" t="n">
-        <v>6871374</v>
+        <v>6870981</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4679,6 +4678,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -7145,10 +7145,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131523981</v>
+        <v>131523842</v>
       </c>
       <c r="B65" t="n">
-        <v>79254</v>
+        <v>79844</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7156,21 +7156,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>370036</v>
+        <v>370085</v>
       </c>
       <c r="R65" t="n">
-        <v>6871407</v>
+        <v>6871463</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7242,10 +7242,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131523842</v>
+        <v>131523981</v>
       </c>
       <c r="B66" t="n">
-        <v>79844</v>
+        <v>79254</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7253,21 +7253,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7277,10 +7277,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>370085</v>
+        <v>370036</v>
       </c>
       <c r="R66" t="n">
-        <v>6871463</v>
+        <v>6871407</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7436,37 +7436,43 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131523855</v>
+        <v>131523936</v>
       </c>
       <c r="B68" t="n">
-        <v>79349</v>
+        <v>8453</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>967</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7474,10 +7480,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>370088</v>
+        <v>370347</v>
       </c>
       <c r="R68" t="n">
-        <v>6871179</v>
+        <v>6870585</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7537,53 +7543,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131523876</v>
+        <v>131523848</v>
       </c>
       <c r="B69" t="n">
-        <v>57080</v>
+        <v>79844</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>370067</v>
+        <v>370077</v>
       </c>
       <c r="R69" t="n">
-        <v>6871433</v>
+        <v>6871172</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7616,11 +7614,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska spår i snön</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7647,43 +7640,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131523936</v>
+        <v>131523855</v>
       </c>
       <c r="B70" t="n">
-        <v>8453</v>
+        <v>79349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>967</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7691,10 +7678,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>370347</v>
+        <v>370088</v>
       </c>
       <c r="R70" t="n">
-        <v>6870585</v>
+        <v>6871179</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7754,45 +7741,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131523848</v>
+        <v>131523876</v>
       </c>
       <c r="B71" t="n">
-        <v>79844</v>
+        <v>57080</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vassbo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>370077</v>
+        <v>370067</v>
       </c>
       <c r="R71" t="n">
-        <v>6871172</v>
+        <v>6871433</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7825,6 +7820,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska spår i snön</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 7916-2026 artfynd.xlsx
+++ b/artfynd/A 7916-2026 artfynd.xlsx
@@ -8667,7 +8667,7 @@
         <v>131917730</v>
       </c>
       <c r="B80" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 7916-2026 artfynd.xlsx
+++ b/artfynd/A 7916-2026 artfynd.xlsx
@@ -8667,7 +8667,7 @@
         <v>131917730</v>
       </c>
       <c r="B80" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>131917899</v>
       </c>
       <c r="B81" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 7916-2026 artfynd.xlsx
+++ b/artfynd/A 7916-2026 artfynd.xlsx
@@ -8667,7 +8667,7 @@
         <v>131917730</v>
       </c>
       <c r="B80" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>131917899</v>
       </c>
       <c r="B81" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
